--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260911.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.02%</t>
+          <t>11.22%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.32%</t>
+          <t>10.46%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.77%</t>
+          <t>7.88%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>7.83%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.58%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.39%</t>
+          <t>4.58%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.29%</t>
+          <t>4.20%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.42%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.02%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.64%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.32%</t>
+          <t>2.27%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.23%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>50,160</t>
+          <t>95,263</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>95,263</t>
+          <t>50,160</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>51,310</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>51,310</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1232,73 +1232,73 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>75,174</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>75,174</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1364,51 +1364,51 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1474,46 +1474,46 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>PNW US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>皮那可資本公司</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>16,127</t>
+          <t>13,424</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>PNW US</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>皮那可資本公司</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>13,424</t>
+          <t>16,127</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.25%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>120,860,143</t>
+          <t>129,061,564</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
